--- a/artfynd/A 26733-2024 artfynd.xlsx
+++ b/artfynd/A 26733-2024 artfynd.xlsx
@@ -1564,10 +1564,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118675972</v>
+        <v>118675990</v>
       </c>
       <c r="B10" t="n">
-        <v>89575</v>
+        <v>91783</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1576,25 +1576,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1962</v>
+        <v>4365</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1608,10 +1608,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>741876</v>
+        <v>741384</v>
       </c>
       <c r="R10" t="n">
-        <v>7295224</v>
+        <v>7295367</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1675,10 +1675,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118675973</v>
+        <v>118675984</v>
       </c>
       <c r="B11" t="n">
-        <v>91791</v>
+        <v>91823</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1687,25 +1687,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4366</v>
+        <v>5449</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1719,10 +1719,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>741771</v>
+        <v>741677</v>
       </c>
       <c r="R11" t="n">
-        <v>7295246</v>
+        <v>7295301</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1749,12 +1749,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2023-09-25</t>
+          <t>2023-09-28</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2023-09-25</t>
+          <t>2023-09-28</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -1897,10 +1897,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118675975</v>
+        <v>118675981</v>
       </c>
       <c r="B13" t="n">
-        <v>89999</v>
+        <v>91773</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1909,25 +1909,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2051</v>
+        <v>4362</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rotfingersvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Ramaria boreimaxima</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; M.Toivonen</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1941,10 +1941,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>741729</v>
+        <v>741752</v>
       </c>
       <c r="R13" t="n">
-        <v>7295267</v>
+        <v>7295263</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1971,12 +1971,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2023-09-25</t>
+          <t>2023-09-28</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2023-09-25</t>
+          <t>2023-09-28</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2008,10 +2008,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118675979</v>
+        <v>118675980</v>
       </c>
       <c r="B14" t="n">
-        <v>89575</v>
+        <v>91802</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2024,21 +2024,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1962</v>
+        <v>5966</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2055,7 +2055,7 @@
         <v>741829</v>
       </c>
       <c r="R14" t="n">
-        <v>7295244</v>
+        <v>7295237</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2230,10 +2230,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118675984</v>
+        <v>118675974</v>
       </c>
       <c r="B16" t="n">
-        <v>91823</v>
+        <v>91795</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2246,21 +2246,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5449</v>
+        <v>2059</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2274,10 +2274,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>741677</v>
+        <v>741729</v>
       </c>
       <c r="R16" t="n">
-        <v>7295301</v>
+        <v>7295267</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2304,12 +2304,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
+          <t>2023-09-25</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
+          <t>2023-09-25</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -2341,10 +2341,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118675970</v>
+        <v>118675971</v>
       </c>
       <c r="B17" t="n">
-        <v>78220</v>
+        <v>91802</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2357,21 +2357,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6446</v>
+        <v>5966</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>741875</v>
+        <v>741876</v>
       </c>
       <c r="R17" t="n">
-        <v>7295226</v>
+        <v>7295224</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2452,10 +2452,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118675971</v>
+        <v>118675973</v>
       </c>
       <c r="B18" t="n">
-        <v>91802</v>
+        <v>91791</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2464,25 +2464,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5966</v>
+        <v>4366</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2496,10 +2496,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>741876</v>
+        <v>741771</v>
       </c>
       <c r="R18" t="n">
-        <v>7295224</v>
+        <v>7295246</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2563,10 +2563,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118675988</v>
+        <v>118675978</v>
       </c>
       <c r="B19" t="n">
-        <v>91779</v>
+        <v>78220</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2575,25 +2575,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2607,10 +2607,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>741389</v>
+        <v>741900</v>
       </c>
       <c r="R19" t="n">
-        <v>7295360</v>
+        <v>7295228</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2637,12 +2637,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2023-09-25</t>
+          <t>2023-09-28</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2023-09-25</t>
+          <t>2023-09-28</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -2674,10 +2674,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118675986</v>
+        <v>118675987</v>
       </c>
       <c r="B20" t="n">
-        <v>89999</v>
+        <v>91795</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2686,25 +2686,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2051</v>
+        <v>2059</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rotfingersvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Ramaria boreimaxima</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; M.Toivonen</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2718,10 +2718,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>741517</v>
+        <v>741403</v>
       </c>
       <c r="R20" t="n">
-        <v>7295299</v>
+        <v>7295287</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2785,10 +2785,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118675985</v>
+        <v>118675986</v>
       </c>
       <c r="B21" t="n">
-        <v>91771</v>
+        <v>89999</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2797,25 +2797,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4361</v>
+        <v>2051</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Rotfingersvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Ramaria boreimaxima</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Kytöv. &amp; M.Toivonen</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2829,10 +2829,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>741562</v>
+        <v>741517</v>
       </c>
       <c r="R21" t="n">
-        <v>7295281</v>
+        <v>7295299</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2896,10 +2896,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118675980</v>
+        <v>118675972</v>
       </c>
       <c r="B22" t="n">
-        <v>91802</v>
+        <v>89575</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2912,21 +2912,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5966</v>
+        <v>1962</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2940,10 +2940,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>741829</v>
+        <v>741876</v>
       </c>
       <c r="R22" t="n">
-        <v>7295237</v>
+        <v>7295224</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2970,12 +2970,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
+          <t>2023-09-25</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
+          <t>2023-09-25</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -3007,10 +3007,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118675974</v>
+        <v>118675977</v>
       </c>
       <c r="B23" t="n">
-        <v>91795</v>
+        <v>91823</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3023,21 +3023,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2059</v>
+        <v>5449</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -3051,10 +3051,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>741729</v>
+        <v>741692</v>
       </c>
       <c r="R23" t="n">
-        <v>7295267</v>
+        <v>7295282</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3118,10 +3118,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>118675983</v>
+        <v>118675970</v>
       </c>
       <c r="B24" t="n">
-        <v>91791</v>
+        <v>78220</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3130,25 +3130,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4366</v>
+        <v>6446</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3162,10 +3162,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>741729</v>
+        <v>741875</v>
       </c>
       <c r="R24" t="n">
-        <v>7295271</v>
+        <v>7295226</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3192,12 +3192,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
+          <t>2023-09-25</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
+          <t>2023-09-25</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
@@ -3229,10 +3229,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>118675977</v>
+        <v>118675988</v>
       </c>
       <c r="B25" t="n">
-        <v>91823</v>
+        <v>91779</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3241,25 +3241,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3273,10 +3273,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>741692</v>
+        <v>741389</v>
       </c>
       <c r="R25" t="n">
-        <v>7295282</v>
+        <v>7295360</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3451,10 +3451,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>118675981</v>
+        <v>118675979</v>
       </c>
       <c r="B27" t="n">
-        <v>91773</v>
+        <v>89575</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3467,21 +3467,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4362</v>
+        <v>1962</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3495,10 +3495,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>741752</v>
+        <v>741829</v>
       </c>
       <c r="R27" t="n">
-        <v>7295263</v>
+        <v>7295244</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3562,10 +3562,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>118675978</v>
+        <v>118675985</v>
       </c>
       <c r="B28" t="n">
-        <v>78220</v>
+        <v>91771</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3578,21 +3578,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6446</v>
+        <v>4361</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3606,10 +3606,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>741900</v>
+        <v>741562</v>
       </c>
       <c r="R28" t="n">
-        <v>7295228</v>
+        <v>7295281</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3636,12 +3636,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
+          <t>2023-09-25</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
+          <t>2023-09-25</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
@@ -3673,10 +3673,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>118675987</v>
+        <v>118675975</v>
       </c>
       <c r="B29" t="n">
-        <v>91795</v>
+        <v>89999</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3685,25 +3685,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2059</v>
+        <v>2051</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Rotfingersvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Ramaria boreimaxima</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>Kytöv. &amp; M.Toivonen</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3717,10 +3717,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>741403</v>
+        <v>741729</v>
       </c>
       <c r="R29" t="n">
-        <v>7295287</v>
+        <v>7295267</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3784,10 +3784,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>118675990</v>
+        <v>118675983</v>
       </c>
       <c r="B30" t="n">
-        <v>91783</v>
+        <v>91791</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3796,25 +3796,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4365</v>
+        <v>4366</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3828,10 +3828,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>741384</v>
+        <v>741729</v>
       </c>
       <c r="R30" t="n">
-        <v>7295367</v>
+        <v>7295271</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3858,12 +3858,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2023-09-25</t>
+          <t>2023-09-28</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2023-09-25</t>
+          <t>2023-09-28</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
@@ -3895,10 +3895,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>118767584</v>
+        <v>118767587</v>
       </c>
       <c r="B31" t="n">
-        <v>56502</v>
+        <v>91779</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3911,31 +3911,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100138</v>
+        <v>4364</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3943,10 +3946,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>741762</v>
+        <v>741878</v>
       </c>
       <c r="R31" t="n">
-        <v>7295230</v>
+        <v>7295261</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3981,12 +3984,18 @@
           <t>2024-07-28</t>
         </is>
       </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Fjolårssvamp med vit mycelmatta</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -4005,10 +4014,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>118767587</v>
+        <v>118767584</v>
       </c>
       <c r="B32" t="n">
-        <v>91779</v>
+        <v>56502</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4021,34 +4030,31 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4364</v>
+        <v>100138</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4056,10 +4062,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>741878</v>
+        <v>741762</v>
       </c>
       <c r="R32" t="n">
-        <v>7295261</v>
+        <v>7295230</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4094,18 +4100,12 @@
           <t>2024-07-28</t>
         </is>
       </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Fjolårssvamp med vit mycelmatta</t>
-        </is>
-      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 26733-2024 artfynd.xlsx
+++ b/artfynd/A 26733-2024 artfynd.xlsx
@@ -2674,10 +2674,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118675987</v>
+        <v>118675977</v>
       </c>
       <c r="B20" t="n">
-        <v>91795</v>
+        <v>91823</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2690,21 +2690,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2059</v>
+        <v>5449</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2718,10 +2718,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>741403</v>
+        <v>741692</v>
       </c>
       <c r="R20" t="n">
-        <v>7295287</v>
+        <v>7295282</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2785,10 +2785,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118675986</v>
+        <v>118675987</v>
       </c>
       <c r="B21" t="n">
-        <v>89999</v>
+        <v>91795</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2797,25 +2797,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2051</v>
+        <v>2059</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rotfingersvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Ramaria boreimaxima</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; M.Toivonen</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2829,10 +2829,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>741517</v>
+        <v>741403</v>
       </c>
       <c r="R21" t="n">
-        <v>7295299</v>
+        <v>7295287</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2896,10 +2896,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118675972</v>
+        <v>118675986</v>
       </c>
       <c r="B22" t="n">
-        <v>89575</v>
+        <v>89999</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2908,25 +2908,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1962</v>
+        <v>2051</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Rotfingersvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Ramaria boreimaxima</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>Kytöv. &amp; M.Toivonen</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2940,10 +2940,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>741876</v>
+        <v>741517</v>
       </c>
       <c r="R22" t="n">
-        <v>7295224</v>
+        <v>7295299</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3007,10 +3007,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118675977</v>
+        <v>118675972</v>
       </c>
       <c r="B23" t="n">
-        <v>91823</v>
+        <v>89575</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3023,21 +3023,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5449</v>
+        <v>1962</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -3051,10 +3051,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>741692</v>
+        <v>741876</v>
       </c>
       <c r="R23" t="n">
-        <v>7295282</v>
+        <v>7295224</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>

--- a/artfynd/A 26733-2024 artfynd.xlsx
+++ b/artfynd/A 26733-2024 artfynd.xlsx
@@ -1564,10 +1564,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118675990</v>
+        <v>118675979</v>
       </c>
       <c r="B10" t="n">
-        <v>91783</v>
+        <v>89575</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1576,25 +1576,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4365</v>
+        <v>1962</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1608,10 +1608,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>741384</v>
+        <v>741829</v>
       </c>
       <c r="R10" t="n">
-        <v>7295367</v>
+        <v>7295244</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2023-09-25</t>
+          <t>2023-09-28</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2023-09-25</t>
+          <t>2023-09-28</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1675,10 +1675,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118675984</v>
+        <v>118675983</v>
       </c>
       <c r="B11" t="n">
-        <v>91823</v>
+        <v>91791</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1687,25 +1687,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5449</v>
+        <v>4366</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1719,10 +1719,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>741677</v>
+        <v>741729</v>
       </c>
       <c r="R11" t="n">
-        <v>7295301</v>
+        <v>7295271</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1786,10 +1786,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118675989</v>
+        <v>118675969</v>
       </c>
       <c r="B12" t="n">
-        <v>91825</v>
+        <v>91802</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1798,25 +1798,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>232140</v>
+        <v>5966</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1830,10 +1830,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>741385</v>
+        <v>741737</v>
       </c>
       <c r="R12" t="n">
-        <v>7295367</v>
+        <v>7295240</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1897,10 +1897,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118675981</v>
+        <v>118675987</v>
       </c>
       <c r="B13" t="n">
-        <v>91773</v>
+        <v>91795</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1913,21 +1913,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4362</v>
+        <v>2059</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1941,10 +1941,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>741752</v>
+        <v>741403</v>
       </c>
       <c r="R13" t="n">
-        <v>7295263</v>
+        <v>7295287</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1971,12 +1971,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
+          <t>2023-09-25</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
+          <t>2023-09-25</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2008,10 +2008,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118675980</v>
+        <v>118675978</v>
       </c>
       <c r="B14" t="n">
-        <v>91802</v>
+        <v>78220</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2024,21 +2024,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5966</v>
+        <v>6446</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2052,10 +2052,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>741829</v>
+        <v>741900</v>
       </c>
       <c r="R14" t="n">
-        <v>7295237</v>
+        <v>7295228</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2119,10 +2119,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118675991</v>
+        <v>118675984</v>
       </c>
       <c r="B15" t="n">
-        <v>91771</v>
+        <v>91823</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2135,21 +2135,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4361</v>
+        <v>5449</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2163,10 +2163,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>741370</v>
+        <v>741677</v>
       </c>
       <c r="R15" t="n">
-        <v>7295400</v>
+        <v>7295301</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2193,12 +2193,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2023-09-25</t>
+          <t>2023-09-28</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2023-09-25</t>
+          <t>2023-09-28</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -2230,10 +2230,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118675974</v>
+        <v>118675980</v>
       </c>
       <c r="B16" t="n">
-        <v>91795</v>
+        <v>91802</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2246,21 +2246,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2059</v>
+        <v>5966</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2274,10 +2274,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>741729</v>
+        <v>741829</v>
       </c>
       <c r="R16" t="n">
-        <v>7295267</v>
+        <v>7295237</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2304,12 +2304,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2023-09-25</t>
+          <t>2023-09-28</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2023-09-25</t>
+          <t>2023-09-28</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -2341,10 +2341,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118675971</v>
+        <v>118675986</v>
       </c>
       <c r="B17" t="n">
-        <v>91802</v>
+        <v>89999</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2353,25 +2353,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5966</v>
+        <v>2051</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Rotfingersvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Ramaria boreimaxima</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Kytöv. &amp; M.Toivonen</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>741876</v>
+        <v>741517</v>
       </c>
       <c r="R17" t="n">
-        <v>7295224</v>
+        <v>7295299</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2452,10 +2452,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118675973</v>
+        <v>118675972</v>
       </c>
       <c r="B18" t="n">
-        <v>91791</v>
+        <v>89575</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2464,25 +2464,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4366</v>
+        <v>1962</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2496,10 +2496,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>741771</v>
+        <v>741876</v>
       </c>
       <c r="R18" t="n">
-        <v>7295246</v>
+        <v>7295224</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2563,10 +2563,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118675978</v>
+        <v>118675989</v>
       </c>
       <c r="B19" t="n">
-        <v>78220</v>
+        <v>91825</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2575,25 +2575,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6446</v>
+        <v>232140</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tajgataggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phellodon secretus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Niemelä &amp; Kinnunen</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2607,10 +2607,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>741900</v>
+        <v>741385</v>
       </c>
       <c r="R19" t="n">
-        <v>7295228</v>
+        <v>7295367</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2637,12 +2637,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
+          <t>2023-09-25</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
+          <t>2023-09-25</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -2674,10 +2674,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118675977</v>
+        <v>118675981</v>
       </c>
       <c r="B20" t="n">
-        <v>91823</v>
+        <v>91773</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2690,21 +2690,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5449</v>
+        <v>4362</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2718,10 +2718,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>741692</v>
+        <v>741752</v>
       </c>
       <c r="R20" t="n">
-        <v>7295282</v>
+        <v>7295263</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2748,12 +2748,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2023-09-25</t>
+          <t>2023-09-28</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2023-09-25</t>
+          <t>2023-09-28</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -2785,10 +2785,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118675987</v>
+        <v>118675988</v>
       </c>
       <c r="B21" t="n">
-        <v>91795</v>
+        <v>91779</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2797,25 +2797,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2829,10 +2829,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>741403</v>
+        <v>741389</v>
       </c>
       <c r="R21" t="n">
-        <v>7295287</v>
+        <v>7295360</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2896,10 +2896,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118675986</v>
+        <v>118675974</v>
       </c>
       <c r="B22" t="n">
-        <v>89999</v>
+        <v>91795</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2908,25 +2908,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2051</v>
+        <v>2059</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rotfingersvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Ramaria boreimaxima</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; M.Toivonen</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2940,10 +2940,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>741517</v>
+        <v>741729</v>
       </c>
       <c r="R22" t="n">
-        <v>7295299</v>
+        <v>7295267</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3007,10 +3007,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118675972</v>
+        <v>118675971</v>
       </c>
       <c r="B23" t="n">
-        <v>89575</v>
+        <v>91802</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3023,21 +3023,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1962</v>
+        <v>5966</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -3118,10 +3118,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>118675970</v>
+        <v>118675973</v>
       </c>
       <c r="B24" t="n">
-        <v>78220</v>
+        <v>91791</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3130,25 +3130,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6446</v>
+        <v>4366</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3162,10 +3162,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>741875</v>
+        <v>741771</v>
       </c>
       <c r="R24" t="n">
-        <v>7295226</v>
+        <v>7295246</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3229,10 +3229,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>118675988</v>
+        <v>118675991</v>
       </c>
       <c r="B25" t="n">
-        <v>91779</v>
+        <v>91771</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3241,25 +3241,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3273,10 +3273,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>741389</v>
+        <v>741370</v>
       </c>
       <c r="R25" t="n">
-        <v>7295360</v>
+        <v>7295400</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3340,10 +3340,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>118675969</v>
+        <v>118675970</v>
       </c>
       <c r="B26" t="n">
-        <v>91802</v>
+        <v>78220</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3356,21 +3356,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5966</v>
+        <v>6446</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -3384,10 +3384,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>741737</v>
+        <v>741875</v>
       </c>
       <c r="R26" t="n">
-        <v>7295240</v>
+        <v>7295226</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3451,10 +3451,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>118675979</v>
+        <v>118675977</v>
       </c>
       <c r="B27" t="n">
-        <v>89575</v>
+        <v>91823</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3467,21 +3467,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1962</v>
+        <v>5449</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3495,10 +3495,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>741829</v>
+        <v>741692</v>
       </c>
       <c r="R27" t="n">
-        <v>7295244</v>
+        <v>7295282</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3525,12 +3525,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
+          <t>2023-09-25</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
+          <t>2023-09-25</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
@@ -3562,10 +3562,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>118675985</v>
+        <v>118675975</v>
       </c>
       <c r="B28" t="n">
-        <v>91771</v>
+        <v>89999</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3574,25 +3574,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4361</v>
+        <v>2051</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Rotfingersvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Ramaria boreimaxima</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Kytöv. &amp; M.Toivonen</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3606,10 +3606,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>741562</v>
+        <v>741729</v>
       </c>
       <c r="R28" t="n">
-        <v>7295281</v>
+        <v>7295267</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3673,10 +3673,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>118675975</v>
+        <v>118675990</v>
       </c>
       <c r="B29" t="n">
-        <v>89999</v>
+        <v>91783</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3689,21 +3689,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2051</v>
+        <v>4365</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rotfingersvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Ramaria boreimaxima</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; M.Toivonen</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3717,10 +3717,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>741729</v>
+        <v>741384</v>
       </c>
       <c r="R29" t="n">
-        <v>7295267</v>
+        <v>7295367</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3784,10 +3784,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>118675983</v>
+        <v>118675985</v>
       </c>
       <c r="B30" t="n">
-        <v>91791</v>
+        <v>91771</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3796,25 +3796,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4366</v>
+        <v>4361</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3828,10 +3828,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>741729</v>
+        <v>741562</v>
       </c>
       <c r="R30" t="n">
-        <v>7295271</v>
+        <v>7295281</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3858,12 +3858,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
+          <t>2023-09-25</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
+          <t>2023-09-25</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
@@ -3895,7 +3895,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>118767587</v>
+        <v>118767586</v>
       </c>
       <c r="B31" t="n">
         <v>91779</v>
@@ -3946,10 +3946,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>741878</v>
+        <v>741962</v>
       </c>
       <c r="R31" t="n">
-        <v>7295261</v>
+        <v>7295247</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4014,10 +4014,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>118767584</v>
+        <v>118767587</v>
       </c>
       <c r="B32" t="n">
-        <v>56502</v>
+        <v>91779</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4030,31 +4030,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100138</v>
+        <v>4364</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4062,10 +4065,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>741762</v>
+        <v>741878</v>
       </c>
       <c r="R32" t="n">
-        <v>7295230</v>
+        <v>7295261</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4100,12 +4103,18 @@
           <t>2024-07-28</t>
         </is>
       </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Fjolårssvamp med vit mycelmatta</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4124,10 +4133,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>118767586</v>
+        <v>118767584</v>
       </c>
       <c r="B33" t="n">
-        <v>91779</v>
+        <v>56502</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4140,34 +4149,31 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4364</v>
+        <v>100138</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4175,10 +4181,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>741962</v>
+        <v>741762</v>
       </c>
       <c r="R33" t="n">
-        <v>7295247</v>
+        <v>7295230</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4213,18 +4219,12 @@
           <t>2024-07-28</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Fjolårssvamp med vit mycelmatta</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 26733-2024 artfynd.xlsx
+++ b/artfynd/A 26733-2024 artfynd.xlsx
@@ -1564,10 +1564,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118675979</v>
+        <v>118675977</v>
       </c>
       <c r="B10" t="n">
-        <v>89575</v>
+        <v>91830</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1580,21 +1580,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1962</v>
+        <v>5449</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1608,10 +1608,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>741829</v>
+        <v>741692</v>
       </c>
       <c r="R10" t="n">
-        <v>7295244</v>
+        <v>7295282</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
+          <t>2023-09-25</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
+          <t>2023-09-25</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1675,10 +1675,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118675983</v>
+        <v>118675975</v>
       </c>
       <c r="B11" t="n">
-        <v>91791</v>
+        <v>90006</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1687,25 +1687,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4366</v>
+        <v>2051</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Rotfingersvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Ramaria boreimaxima</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>Kytöv. &amp; M.Toivonen</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1722,7 +1722,7 @@
         <v>741729</v>
       </c>
       <c r="R11" t="n">
-        <v>7295271</v>
+        <v>7295267</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1749,12 +1749,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
+          <t>2023-09-25</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
+          <t>2023-09-25</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -1786,10 +1786,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118675969</v>
+        <v>118675983</v>
       </c>
       <c r="B12" t="n">
-        <v>91802</v>
+        <v>91798</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1798,25 +1798,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5966</v>
+        <v>4366</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1830,10 +1830,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>741737</v>
+        <v>741729</v>
       </c>
       <c r="R12" t="n">
-        <v>7295240</v>
+        <v>7295271</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1860,12 +1860,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2023-09-25</t>
+          <t>2023-09-28</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2023-09-25</t>
+          <t>2023-09-28</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -1897,10 +1897,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118675987</v>
+        <v>118675979</v>
       </c>
       <c r="B13" t="n">
-        <v>91795</v>
+        <v>89582</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1913,21 +1913,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2059</v>
+        <v>1962</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1941,10 +1941,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>741403</v>
+        <v>741829</v>
       </c>
       <c r="R13" t="n">
-        <v>7295287</v>
+        <v>7295244</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1971,12 +1971,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2023-09-25</t>
+          <t>2023-09-28</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2023-09-25</t>
+          <t>2023-09-28</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2008,10 +2008,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118675978</v>
+        <v>118675973</v>
       </c>
       <c r="B14" t="n">
-        <v>78220</v>
+        <v>91798</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2020,25 +2020,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6446</v>
+        <v>4366</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2052,10 +2052,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>741900</v>
+        <v>741771</v>
       </c>
       <c r="R14" t="n">
-        <v>7295228</v>
+        <v>7295246</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2082,12 +2082,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
+          <t>2023-09-25</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
+          <t>2023-09-25</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2119,10 +2119,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118675984</v>
+        <v>118675969</v>
       </c>
       <c r="B15" t="n">
-        <v>91823</v>
+        <v>91809</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2135,21 +2135,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5449</v>
+        <v>5966</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2163,10 +2163,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>741677</v>
+        <v>741737</v>
       </c>
       <c r="R15" t="n">
-        <v>7295301</v>
+        <v>7295240</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2193,12 +2193,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
+          <t>2023-09-25</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
+          <t>2023-09-25</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -2230,10 +2230,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118675980</v>
+        <v>118675990</v>
       </c>
       <c r="B16" t="n">
-        <v>91802</v>
+        <v>91790</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2242,25 +2242,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5966</v>
+        <v>4365</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2274,10 +2274,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>741829</v>
+        <v>741384</v>
       </c>
       <c r="R16" t="n">
-        <v>7295237</v>
+        <v>7295367</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2304,12 +2304,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
+          <t>2023-09-25</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
+          <t>2023-09-25</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -2341,10 +2341,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118675986</v>
+        <v>118675989</v>
       </c>
       <c r="B17" t="n">
-        <v>89999</v>
+        <v>91832</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2357,21 +2357,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2051</v>
+        <v>232140</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rotfingersvamp</t>
+          <t>Tajgataggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Ramaria boreimaxima</t>
+          <t>Phellodon secretus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; M.Toivonen</t>
+          <t>Niemelä &amp; Kinnunen</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>741517</v>
+        <v>741385</v>
       </c>
       <c r="R17" t="n">
-        <v>7295299</v>
+        <v>7295367</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2452,10 +2452,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118675972</v>
+        <v>118675988</v>
       </c>
       <c r="B18" t="n">
-        <v>89575</v>
+        <v>91786</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2464,25 +2464,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1962</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2496,10 +2496,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>741876</v>
+        <v>741389</v>
       </c>
       <c r="R18" t="n">
-        <v>7295224</v>
+        <v>7295360</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2563,10 +2563,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118675989</v>
+        <v>118675972</v>
       </c>
       <c r="B19" t="n">
-        <v>91825</v>
+        <v>89582</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2575,25 +2575,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>232140</v>
+        <v>1962</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2607,10 +2607,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>741385</v>
+        <v>741876</v>
       </c>
       <c r="R19" t="n">
-        <v>7295367</v>
+        <v>7295224</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2674,10 +2674,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118675981</v>
+        <v>118675971</v>
       </c>
       <c r="B20" t="n">
-        <v>91773</v>
+        <v>91809</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2690,21 +2690,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4362</v>
+        <v>5966</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2718,10 +2718,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>741752</v>
+        <v>741876</v>
       </c>
       <c r="R20" t="n">
-        <v>7295263</v>
+        <v>7295224</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2748,12 +2748,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
+          <t>2023-09-25</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
+          <t>2023-09-25</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -2785,10 +2785,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118675988</v>
+        <v>118675978</v>
       </c>
       <c r="B21" t="n">
-        <v>91779</v>
+        <v>78227</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2797,25 +2797,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2829,10 +2829,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>741389</v>
+        <v>741900</v>
       </c>
       <c r="R21" t="n">
-        <v>7295360</v>
+        <v>7295228</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2859,12 +2859,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2023-09-25</t>
+          <t>2023-09-28</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2023-09-25</t>
+          <t>2023-09-28</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -2896,10 +2896,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118675974</v>
+        <v>118675987</v>
       </c>
       <c r="B22" t="n">
-        <v>91795</v>
+        <v>91802</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2940,10 +2940,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>741729</v>
+        <v>741403</v>
       </c>
       <c r="R22" t="n">
-        <v>7295267</v>
+        <v>7295287</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3007,10 +3007,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118675971</v>
+        <v>118675980</v>
       </c>
       <c r="B23" t="n">
-        <v>91802</v>
+        <v>91809</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3051,10 +3051,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>741876</v>
+        <v>741829</v>
       </c>
       <c r="R23" t="n">
-        <v>7295224</v>
+        <v>7295237</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3081,12 +3081,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2023-09-25</t>
+          <t>2023-09-28</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2023-09-25</t>
+          <t>2023-09-28</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -3118,10 +3118,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>118675973</v>
+        <v>118675991</v>
       </c>
       <c r="B24" t="n">
-        <v>91791</v>
+        <v>91778</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3130,25 +3130,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4366</v>
+        <v>4361</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3162,10 +3162,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>741771</v>
+        <v>741370</v>
       </c>
       <c r="R24" t="n">
-        <v>7295246</v>
+        <v>7295400</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3229,10 +3229,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>118675991</v>
+        <v>118675974</v>
       </c>
       <c r="B25" t="n">
-        <v>91771</v>
+        <v>91802</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3245,21 +3245,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4361</v>
+        <v>2059</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3273,10 +3273,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>741370</v>
+        <v>741729</v>
       </c>
       <c r="R25" t="n">
-        <v>7295400</v>
+        <v>7295267</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3340,10 +3340,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>118675970</v>
+        <v>118675985</v>
       </c>
       <c r="B26" t="n">
-        <v>78220</v>
+        <v>91778</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3356,21 +3356,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6446</v>
+        <v>4361</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -3384,10 +3384,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>741875</v>
+        <v>741562</v>
       </c>
       <c r="R26" t="n">
-        <v>7295226</v>
+        <v>7295281</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3451,10 +3451,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>118675977</v>
+        <v>118675970</v>
       </c>
       <c r="B27" t="n">
-        <v>91823</v>
+        <v>78227</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3467,21 +3467,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5449</v>
+        <v>6446</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3495,10 +3495,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>741692</v>
+        <v>741875</v>
       </c>
       <c r="R27" t="n">
-        <v>7295282</v>
+        <v>7295226</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3562,10 +3562,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>118675975</v>
+        <v>118675986</v>
       </c>
       <c r="B28" t="n">
-        <v>89999</v>
+        <v>90006</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3606,10 +3606,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>741729</v>
+        <v>741517</v>
       </c>
       <c r="R28" t="n">
-        <v>7295267</v>
+        <v>7295299</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3673,10 +3673,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>118675990</v>
+        <v>118675984</v>
       </c>
       <c r="B29" t="n">
-        <v>91783</v>
+        <v>91830</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3685,25 +3685,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4365</v>
+        <v>5449</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3717,10 +3717,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>741384</v>
+        <v>741677</v>
       </c>
       <c r="R29" t="n">
-        <v>7295367</v>
+        <v>7295301</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3747,12 +3747,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2023-09-25</t>
+          <t>2023-09-28</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2023-09-25</t>
+          <t>2023-09-28</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
@@ -3784,10 +3784,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>118675985</v>
+        <v>118675981</v>
       </c>
       <c r="B30" t="n">
-        <v>91771</v>
+        <v>91780</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3800,21 +3800,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3828,10 +3828,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>741562</v>
+        <v>741752</v>
       </c>
       <c r="R30" t="n">
-        <v>7295281</v>
+        <v>7295263</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3858,12 +3858,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2023-09-25</t>
+          <t>2023-09-28</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2023-09-25</t>
+          <t>2023-09-28</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
@@ -3898,7 +3898,7 @@
         <v>118767586</v>
       </c>
       <c r="B31" t="n">
-        <v>91779</v>
+        <v>91786</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4017,7 +4017,7 @@
         <v>118767587</v>
       </c>
       <c r="B32" t="n">
-        <v>91779</v>
+        <v>91786</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>

--- a/artfynd/A 26733-2024 artfynd.xlsx
+++ b/artfynd/A 26733-2024 artfynd.xlsx
@@ -2008,10 +2008,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118675973</v>
+        <v>118675969</v>
       </c>
       <c r="B14" t="n">
-        <v>91798</v>
+        <v>91809</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2020,25 +2020,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4366</v>
+        <v>5966</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2052,10 +2052,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>741771</v>
+        <v>741737</v>
       </c>
       <c r="R14" t="n">
-        <v>7295246</v>
+        <v>7295240</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2119,10 +2119,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118675969</v>
+        <v>118675973</v>
       </c>
       <c r="B15" t="n">
-        <v>91809</v>
+        <v>91798</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2131,25 +2131,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5966</v>
+        <v>4366</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2163,10 +2163,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>741737</v>
+        <v>741771</v>
       </c>
       <c r="R15" t="n">
-        <v>7295240</v>
+        <v>7295246</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>

--- a/artfynd/A 26733-2024 artfynd.xlsx
+++ b/artfynd/A 26733-2024 artfynd.xlsx
@@ -1564,10 +1564,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118675977</v>
+        <v>118675978</v>
       </c>
       <c r="B10" t="n">
-        <v>91830</v>
+        <v>78227</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1580,21 +1580,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5449</v>
+        <v>6446</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1608,10 +1608,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>741692</v>
+        <v>741900</v>
       </c>
       <c r="R10" t="n">
-        <v>7295282</v>
+        <v>7295228</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2023-09-25</t>
+          <t>2023-09-28</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2023-09-25</t>
+          <t>2023-09-28</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1675,10 +1675,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118675975</v>
+        <v>118675970</v>
       </c>
       <c r="B11" t="n">
-        <v>90006</v>
+        <v>78227</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1687,25 +1687,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2051</v>
+        <v>6446</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rotfingersvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Ramaria boreimaxima</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; M.Toivonen</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1719,10 +1719,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>741729</v>
+        <v>741875</v>
       </c>
       <c r="R11" t="n">
-        <v>7295267</v>
+        <v>7295226</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1786,10 +1786,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118675983</v>
+        <v>118675984</v>
       </c>
       <c r="B12" t="n">
-        <v>91798</v>
+        <v>91830</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1798,25 +1798,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4366</v>
+        <v>5449</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1830,10 +1830,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>741729</v>
+        <v>741677</v>
       </c>
       <c r="R12" t="n">
-        <v>7295271</v>
+        <v>7295301</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1897,10 +1897,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118675979</v>
+        <v>118675985</v>
       </c>
       <c r="B13" t="n">
-        <v>89582</v>
+        <v>91778</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1913,21 +1913,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1962</v>
+        <v>4361</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1941,10 +1941,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>741829</v>
+        <v>741562</v>
       </c>
       <c r="R13" t="n">
-        <v>7295244</v>
+        <v>7295281</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1971,12 +1971,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
+          <t>2023-09-25</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
+          <t>2023-09-25</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2008,10 +2008,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118675969</v>
+        <v>118675988</v>
       </c>
       <c r="B14" t="n">
-        <v>91809</v>
+        <v>91786</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2020,25 +2020,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2052,10 +2052,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>741737</v>
+        <v>741389</v>
       </c>
       <c r="R14" t="n">
-        <v>7295240</v>
+        <v>7295360</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2119,10 +2119,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118675973</v>
+        <v>118675987</v>
       </c>
       <c r="B15" t="n">
-        <v>91798</v>
+        <v>91802</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2131,25 +2131,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4366</v>
+        <v>2059</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2163,10 +2163,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>741771</v>
+        <v>741403</v>
       </c>
       <c r="R15" t="n">
-        <v>7295246</v>
+        <v>7295287</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2230,10 +2230,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118675990</v>
+        <v>118675975</v>
       </c>
       <c r="B16" t="n">
-        <v>91790</v>
+        <v>90006</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2246,21 +2246,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4365</v>
+        <v>2051</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Rotfingersvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Ramaria boreimaxima</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>Kytöv. &amp; M.Toivonen</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2274,10 +2274,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>741384</v>
+        <v>741729</v>
       </c>
       <c r="R16" t="n">
-        <v>7295367</v>
+        <v>7295267</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2341,10 +2341,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118675989</v>
+        <v>118675986</v>
       </c>
       <c r="B17" t="n">
-        <v>91832</v>
+        <v>90006</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2357,21 +2357,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>232140</v>
+        <v>2051</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Rotfingersvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Ramaria boreimaxima</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
+          <t>Kytöv. &amp; M.Toivonen</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>741385</v>
+        <v>741517</v>
       </c>
       <c r="R17" t="n">
-        <v>7295367</v>
+        <v>7295299</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2452,10 +2452,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118675988</v>
+        <v>118675981</v>
       </c>
       <c r="B18" t="n">
-        <v>91786</v>
+        <v>91780</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2464,25 +2464,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2496,10 +2496,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>741389</v>
+        <v>741752</v>
       </c>
       <c r="R18" t="n">
-        <v>7295360</v>
+        <v>7295263</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2526,12 +2526,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2023-09-25</t>
+          <t>2023-09-28</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2023-09-25</t>
+          <t>2023-09-28</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -2563,10 +2563,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118675972</v>
+        <v>118675969</v>
       </c>
       <c r="B19" t="n">
-        <v>89582</v>
+        <v>91809</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2579,21 +2579,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1962</v>
+        <v>5966</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2607,10 +2607,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>741876</v>
+        <v>741737</v>
       </c>
       <c r="R19" t="n">
-        <v>7295224</v>
+        <v>7295240</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2674,10 +2674,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118675971</v>
+        <v>118675972</v>
       </c>
       <c r="B20" t="n">
-        <v>91809</v>
+        <v>89582</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2690,21 +2690,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5966</v>
+        <v>1962</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2785,10 +2785,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118675978</v>
+        <v>118675983</v>
       </c>
       <c r="B21" t="n">
-        <v>78227</v>
+        <v>91798</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2797,25 +2797,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6446</v>
+        <v>4366</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2829,10 +2829,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>741900</v>
+        <v>741729</v>
       </c>
       <c r="R21" t="n">
-        <v>7295228</v>
+        <v>7295271</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2896,10 +2896,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118675987</v>
+        <v>118675971</v>
       </c>
       <c r="B22" t="n">
-        <v>91802</v>
+        <v>91809</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2912,21 +2912,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2059</v>
+        <v>5966</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2940,10 +2940,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>741403</v>
+        <v>741876</v>
       </c>
       <c r="R22" t="n">
-        <v>7295287</v>
+        <v>7295224</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3007,10 +3007,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118675980</v>
+        <v>118675989</v>
       </c>
       <c r="B23" t="n">
-        <v>91809</v>
+        <v>91832</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3019,25 +3019,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5966</v>
+        <v>232140</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tajgataggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Phellodon secretus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Niemelä &amp; Kinnunen</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -3051,10 +3051,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>741829</v>
+        <v>741385</v>
       </c>
       <c r="R23" t="n">
-        <v>7295237</v>
+        <v>7295367</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3081,12 +3081,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
+          <t>2023-09-25</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
+          <t>2023-09-25</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -3229,10 +3229,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>118675974</v>
+        <v>118675979</v>
       </c>
       <c r="B25" t="n">
-        <v>91802</v>
+        <v>89582</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3245,21 +3245,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2059</v>
+        <v>1962</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3273,10 +3273,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>741729</v>
+        <v>741829</v>
       </c>
       <c r="R25" t="n">
-        <v>7295267</v>
+        <v>7295244</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3303,12 +3303,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2023-09-25</t>
+          <t>2023-09-28</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2023-09-25</t>
+          <t>2023-09-28</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
@@ -3340,10 +3340,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>118675985</v>
+        <v>118675980</v>
       </c>
       <c r="B26" t="n">
-        <v>91778</v>
+        <v>91809</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3356,21 +3356,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4361</v>
+        <v>5966</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -3384,10 +3384,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>741562</v>
+        <v>741829</v>
       </c>
       <c r="R26" t="n">
-        <v>7295281</v>
+        <v>7295237</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3414,12 +3414,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2023-09-25</t>
+          <t>2023-09-28</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2023-09-25</t>
+          <t>2023-09-28</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -3451,10 +3451,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>118675970</v>
+        <v>118675974</v>
       </c>
       <c r="B27" t="n">
-        <v>78227</v>
+        <v>91802</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3467,21 +3467,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6446</v>
+        <v>2059</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3495,10 +3495,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>741875</v>
+        <v>741729</v>
       </c>
       <c r="R27" t="n">
-        <v>7295226</v>
+        <v>7295267</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3562,10 +3562,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>118675986</v>
+        <v>118675990</v>
       </c>
       <c r="B28" t="n">
-        <v>90006</v>
+        <v>91790</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3578,21 +3578,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2051</v>
+        <v>4365</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rotfingersvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Ramaria boreimaxima</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; M.Toivonen</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3606,10 +3606,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>741517</v>
+        <v>741384</v>
       </c>
       <c r="R28" t="n">
-        <v>7295299</v>
+        <v>7295367</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3673,10 +3673,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>118675984</v>
+        <v>118675973</v>
       </c>
       <c r="B29" t="n">
-        <v>91830</v>
+        <v>91798</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3685,25 +3685,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5449</v>
+        <v>4366</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3717,10 +3717,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>741677</v>
+        <v>741771</v>
       </c>
       <c r="R29" t="n">
-        <v>7295301</v>
+        <v>7295246</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3747,12 +3747,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
+          <t>2023-09-25</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
+          <t>2023-09-25</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
@@ -3784,10 +3784,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>118675981</v>
+        <v>118675977</v>
       </c>
       <c r="B30" t="n">
-        <v>91780</v>
+        <v>91830</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3800,21 +3800,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4362</v>
+        <v>5449</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3828,10 +3828,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>741752</v>
+        <v>741692</v>
       </c>
       <c r="R30" t="n">
-        <v>7295263</v>
+        <v>7295282</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3858,12 +3858,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
+          <t>2023-09-25</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
+          <t>2023-09-25</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">

--- a/artfynd/A 26733-2024 artfynd.xlsx
+++ b/artfynd/A 26733-2024 artfynd.xlsx
@@ -3898,11 +3898,11 @@
         <v>118767584</v>
       </c>
       <c r="B31" t="n">
-        <v>56504</v>
+        <v>56593</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">

--- a/artfynd/A 26733-2024 artfynd.xlsx
+++ b/artfynd/A 26733-2024 artfynd.xlsx
@@ -3898,7 +3898,7 @@
         <v>118767584</v>
       </c>
       <c r="B31" t="n">
-        <v>56593</v>
+        <v>56594</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>

--- a/artfynd/A 26733-2024 artfynd.xlsx
+++ b/artfynd/A 26733-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY33"/>
+  <dimension ref="A1:AY31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>110049043</v>
       </c>
       <c r="B2" t="n">
-        <v>88476</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90932</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>741887.9288783269</v>
+        <v>741888</v>
       </c>
       <c r="R2" t="n">
-        <v>7295220.194279185</v>
+        <v>7295220</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2022-10-07</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-10-07</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,37 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113888853</v>
+        <v>113888851</v>
       </c>
       <c r="B3" t="n">
-        <v>91617</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90932</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4366</v>
+        <v>1962</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -831,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>741744</v>
+        <v>741828</v>
       </c>
       <c r="R3" t="n">
-        <v>7295260</v>
+        <v>7295240</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -898,15 +878,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113888852</v>
+        <v>118675972</v>
       </c>
       <c r="B4" t="n">
-        <v>91599</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90932</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -914,21 +889,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4362</v>
+        <v>1962</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -942,13 +917,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>741769</v>
+        <v>741876</v>
       </c>
       <c r="R4" t="n">
-        <v>7295250</v>
+        <v>7295224</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1009,15 +984,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113888849</v>
+        <v>118675979</v>
       </c>
       <c r="B5" t="n">
-        <v>78246</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90932</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1025,21 +995,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>1962</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1053,13 +1023,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>741901</v>
+        <v>741829</v>
       </c>
       <c r="R5" t="n">
-        <v>7295230</v>
+        <v>7295244</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1083,12 +1053,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-09-25</t>
+          <t>2023-09-28</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-09-25</t>
+          <t>2023-09-28</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1120,37 +1090,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113888851</v>
+        <v>118675975</v>
       </c>
       <c r="B6" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91394</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1962</v>
+        <v>2051</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Rotfingersvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Ramaria boreimaxima</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>Kytöv. &amp; M.Toivonen</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1164,13 +1129,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>741828</v>
+        <v>741729</v>
       </c>
       <c r="R6" t="n">
-        <v>7295240</v>
+        <v>7295267</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1231,37 +1196,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113888854</v>
+        <v>118675986</v>
       </c>
       <c r="B7" t="n">
-        <v>91649</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91394</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5449</v>
+        <v>2051</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Rotfingersvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Ramaria boreimaxima</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>Kytöv. &amp; M.Toivonen</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1275,13 +1235,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>741678</v>
+        <v>741517</v>
       </c>
       <c r="R7" t="n">
-        <v>7295290</v>
+        <v>7295299</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1342,15 +1302,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113888848</v>
+        <v>118675974</v>
       </c>
       <c r="B8" t="n">
-        <v>91651</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1358,21 +1313,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>232140</v>
+        <v>2059</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1386,13 +1341,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>741479</v>
+        <v>741729</v>
       </c>
       <c r="R8" t="n">
-        <v>7295340</v>
+        <v>7295267</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1453,37 +1408,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113888850</v>
+        <v>118675987</v>
       </c>
       <c r="B9" t="n">
-        <v>91628</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5966</v>
+        <v>2059</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1497,13 +1447,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>741828</v>
+        <v>741403</v>
       </c>
       <c r="R9" t="n">
-        <v>7295240</v>
+        <v>7295287</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1564,15 +1514,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118675984</v>
+        <v>118675985</v>
       </c>
       <c r="B10" t="n">
-        <v>91835</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1580,21 +1525,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5449</v>
+        <v>4361</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1608,10 +1553,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>741677</v>
+        <v>741562</v>
       </c>
       <c r="R10" t="n">
-        <v>7295301</v>
+        <v>7295281</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1638,12 +1583,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
+          <t>2023-09-25</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
+          <t>2023-09-25</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1675,37 +1620,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118675986</v>
+        <v>118675991</v>
       </c>
       <c r="B11" t="n">
-        <v>90008</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2051</v>
+        <v>4361</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rotfingersvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Ramaria boreimaxima</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; M.Toivonen</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1719,10 +1659,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>741517</v>
+        <v>741370</v>
       </c>
       <c r="R11" t="n">
-        <v>7295299</v>
+        <v>7295400</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1786,15 +1726,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118675979</v>
+        <v>113888852</v>
       </c>
       <c r="B12" t="n">
-        <v>89584</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1802,21 +1737,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1962</v>
+        <v>4362</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1830,13 +1765,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>741829</v>
+        <v>741769</v>
       </c>
       <c r="R12" t="n">
-        <v>7295244</v>
+        <v>7295250</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1860,12 +1795,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
+          <t>2023-09-25</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
+          <t>2023-09-25</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -1897,37 +1832,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118675989</v>
+        <v>118675981</v>
       </c>
       <c r="B13" t="n">
-        <v>91837</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>232140</v>
+        <v>4362</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1941,10 +1871,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>741385</v>
+        <v>741752</v>
       </c>
       <c r="R13" t="n">
-        <v>7295367</v>
+        <v>7295263</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1971,12 +1901,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2023-09-25</t>
+          <t>2023-09-28</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2023-09-25</t>
+          <t>2023-09-28</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2008,15 +1938,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118675980</v>
+        <v>118675988</v>
       </c>
       <c r="B14" t="n">
-        <v>91814</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2024,21 +1949,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2052,10 +1977,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>741829</v>
+        <v>741389</v>
       </c>
       <c r="R14" t="n">
-        <v>7295237</v>
+        <v>7295360</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2082,12 +2007,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
+          <t>2023-09-25</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
+          <t>2023-09-25</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2119,15 +2044,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118675972</v>
+        <v>118767586</v>
       </c>
       <c r="B15" t="n">
-        <v>89584</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2135,38 +2055,45 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1962</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Grundsel, Nb</t>
+          <t>Sikträskberget, Nb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>741876</v>
+        <v>741962</v>
       </c>
       <c r="R15" t="n">
-        <v>7295224</v>
+        <v>7295247</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2193,17 +2120,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2023-09-25</t>
+          <t>2024-07-28</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2023-09-25</t>
+          <t>2024-07-28</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>Fjolårssvamp med vit mycelmatta</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2212,33 +2139,29 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118675970</v>
+        <v>118767587</v>
       </c>
       <c r="B16" t="n">
-        <v>78229</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2246,38 +2169,45 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Grundsel, Nb</t>
+          <t>Sikträskberget, Nb</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>741875</v>
+        <v>741878</v>
       </c>
       <c r="R16" t="n">
-        <v>7295226</v>
+        <v>7295261</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2304,17 +2234,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2023-09-25</t>
+          <t>2024-07-28</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2023-09-25</t>
+          <t>2024-07-28</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>Fjolårssvamp med vit mycelmatta</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2323,55 +2253,51 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118675991</v>
+        <v>118675990</v>
       </c>
       <c r="B17" t="n">
-        <v>91783</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93201</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4361</v>
+        <v>4365</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2385,10 +2311,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>741370</v>
+        <v>741384</v>
       </c>
       <c r="R17" t="n">
-        <v>7295400</v>
+        <v>7295367</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2452,54 +2378,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118675973</v>
+        <v>118767585</v>
       </c>
       <c r="B18" t="n">
-        <v>91803</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93201</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4366</v>
+        <v>4365</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst) P.Karst</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Grundsel, Nb</t>
+          <t>Sikträskberget, Nb</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>741771</v>
+        <v>741848</v>
       </c>
       <c r="R18" t="n">
-        <v>7295246</v>
+        <v>7295262</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2526,17 +2443,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2023-09-25</t>
+          <t>2024-07-28</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2023-09-25</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2024-07-28</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2551,27 +2463,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118675978</v>
+        <v>113888853</v>
       </c>
       <c r="B19" t="n">
-        <v>78229</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2579,21 +2486,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6446</v>
+        <v>4366</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2607,13 +2514,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>741900</v>
+        <v>741744</v>
       </c>
       <c r="R19" t="n">
-        <v>7295228</v>
+        <v>7295260</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2637,12 +2544,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
+          <t>2023-09-25</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
+          <t>2023-09-25</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -2674,15 +2581,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118675981</v>
+        <v>118675973</v>
       </c>
       <c r="B20" t="n">
-        <v>91785</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2690,21 +2592,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4362</v>
+        <v>4366</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2718,10 +2620,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>741752</v>
+        <v>741771</v>
       </c>
       <c r="R20" t="n">
-        <v>7295263</v>
+        <v>7295246</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2748,12 +2650,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
+          <t>2023-09-25</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
+          <t>2023-09-25</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -2785,15 +2687,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118675987</v>
+        <v>118675983</v>
       </c>
       <c r="B21" t="n">
-        <v>91807</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2801,21 +2698,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2059</v>
+        <v>4366</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2829,10 +2726,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>741403</v>
+        <v>741729</v>
       </c>
       <c r="R21" t="n">
-        <v>7295287</v>
+        <v>7295271</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2859,12 +2756,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2023-09-25</t>
+          <t>2023-09-28</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2023-09-25</t>
+          <t>2023-09-28</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -2896,15 +2793,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118675977</v>
+        <v>113888850</v>
       </c>
       <c r="B22" t="n">
-        <v>91835</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2912,21 +2804,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5449</v>
+        <v>5966</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2940,13 +2832,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>741692</v>
+        <v>741828</v>
       </c>
       <c r="R22" t="n">
-        <v>7295282</v>
+        <v>7295240</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3007,37 +2899,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118675990</v>
+        <v>118675969</v>
       </c>
       <c r="B23" t="n">
-        <v>91795</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4365</v>
+        <v>5966</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -3051,10 +2938,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>741384</v>
+        <v>741737</v>
       </c>
       <c r="R23" t="n">
-        <v>7295367</v>
+        <v>7295240</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3118,37 +3005,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>118675983</v>
+        <v>118675971</v>
       </c>
       <c r="B24" t="n">
-        <v>91803</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4366</v>
+        <v>5966</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3162,10 +3044,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>741729</v>
+        <v>741876</v>
       </c>
       <c r="R24" t="n">
-        <v>7295271</v>
+        <v>7295224</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3192,12 +3074,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
+          <t>2023-09-25</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
+          <t>2023-09-25</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
@@ -3229,37 +3111,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>118675975</v>
+        <v>118675980</v>
       </c>
       <c r="B25" t="n">
-        <v>90008</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2051</v>
+        <v>5966</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rotfingersvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Ramaria boreimaxima</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; M.Toivonen</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3273,10 +3150,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>741729</v>
+        <v>741829</v>
       </c>
       <c r="R25" t="n">
-        <v>7295267</v>
+        <v>7295237</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3303,12 +3180,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2023-09-25</t>
+          <t>2023-09-28</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2023-09-25</t>
+          <t>2023-09-28</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
@@ -3340,15 +3217,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>118675971</v>
+        <v>113888849</v>
       </c>
       <c r="B26" t="n">
-        <v>91814</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3356,21 +3228,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5966</v>
+        <v>6446</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -3384,13 +3256,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>741876</v>
+        <v>741901</v>
       </c>
       <c r="R26" t="n">
-        <v>7295224</v>
+        <v>7295230</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3451,15 +3323,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>118675985</v>
+        <v>118675970</v>
       </c>
       <c r="B27" t="n">
-        <v>91783</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3467,21 +3334,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4361</v>
+        <v>6446</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3495,10 +3362,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>741562</v>
+        <v>741875</v>
       </c>
       <c r="R27" t="n">
-        <v>7295281</v>
+        <v>7295226</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3562,15 +3429,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>118675974</v>
+        <v>118675978</v>
       </c>
       <c r="B28" t="n">
-        <v>91807</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3578,21 +3440,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2059</v>
+        <v>6446</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3606,10 +3468,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>741729</v>
+        <v>741900</v>
       </c>
       <c r="R28" t="n">
-        <v>7295267</v>
+        <v>7295228</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3636,12 +3498,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2023-09-25</t>
+          <t>2023-09-28</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2023-09-25</t>
+          <t>2023-09-28</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
@@ -3673,15 +3535,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>118675988</v>
+        <v>118767584</v>
       </c>
       <c r="B29" t="n">
-        <v>91791</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3689,38 +3546,42 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4364</v>
+        <v>100138</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Grundsel, Nb</t>
+          <t>Sikträskberget, Nb</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>741389</v>
+        <v>741762</v>
       </c>
       <c r="R29" t="n">
-        <v>7295360</v>
+        <v>7295230</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3747,17 +3608,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2023-09-25</t>
+          <t>2024-07-28</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2023-09-25</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2024-07-28</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3772,49 +3628,44 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>118675969</v>
+        <v>113888848</v>
       </c>
       <c r="B30" t="n">
-        <v>91814</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93228</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5966</v>
+        <v>232140</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tajgataggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Phellodon secretus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Niemelä &amp; Kinnunen</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3828,13 +3679,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>741737</v>
+        <v>741479</v>
       </c>
       <c r="R30" t="n">
-        <v>7295240</v>
+        <v>7295340</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3895,58 +3746,49 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>118767584</v>
+        <v>118675989</v>
       </c>
       <c r="B31" t="n">
-        <v>56688</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>93228</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100138</v>
+        <v>232140</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tajgataggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellodon secretus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
+          <t>Niemelä &amp; Kinnunen</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Sikträskberget, Nb</t>
+          <t>Grundsel, Nb</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>741762</v>
+        <v>741385</v>
       </c>
       <c r="R31" t="n">
-        <v>7295230</v>
+        <v>7295367</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3973,12 +3815,17 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2024-07-28</t>
+          <t>2023-09-25</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2024-07-28</t>
+          <t>2023-09-25</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3993,253 +3840,15 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" t="n">
-        <v>118767587</v>
-      </c>
-      <c r="B32" t="n">
-        <v>91791</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E32" t="n">
-        <v>4364</v>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>Dropptaggsvamp</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>Hydnellum ferrugineum</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
-      <c r="P32" t="inlineStr">
-        <is>
-          <t>Sikträskberget, Nb</t>
-        </is>
-      </c>
-      <c r="Q32" t="n">
-        <v>741878</v>
-      </c>
-      <c r="R32" t="n">
-        <v>7295261</v>
-      </c>
-      <c r="S32" t="n">
-        <v>10</v>
-      </c>
-      <c r="T32" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U32" t="inlineStr">
-        <is>
-          <t>Älvsbyn</t>
-        </is>
-      </c>
-      <c r="V32" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="W32" t="inlineStr">
-        <is>
-          <t>Älvsby</t>
-        </is>
-      </c>
-      <c r="Y32" t="inlineStr">
-        <is>
-          <t>2024-07-28</t>
-        </is>
-      </c>
-      <c r="AA32" t="inlineStr">
-        <is>
-          <t>2024-07-28</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Fjolårssvamp med vit mycelmatta</t>
-        </is>
-      </c>
-      <c r="AD32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF32" t="inlineStr"/>
-      <c r="AG32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT32" t="inlineStr"/>
-      <c r="AW32" t="inlineStr">
-        <is>
-          <t>Linda-Marie Grahn</t>
-        </is>
-      </c>
-      <c r="AX32" t="inlineStr">
-        <is>
-          <t>Linda-Marie Grahn</t>
-        </is>
-      </c>
-      <c r="AY32" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" t="n">
-        <v>118767586</v>
-      </c>
-      <c r="B33" t="n">
-        <v>91791</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E33" t="n">
-        <v>4364</v>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>Dropptaggsvamp</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>Hydnellum ferrugineum</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>Sikträskberget, Nb</t>
-        </is>
-      </c>
-      <c r="Q33" t="n">
-        <v>741962</v>
-      </c>
-      <c r="R33" t="n">
-        <v>7295247</v>
-      </c>
-      <c r="S33" t="n">
-        <v>10</v>
-      </c>
-      <c r="T33" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U33" t="inlineStr">
-        <is>
-          <t>Älvsbyn</t>
-        </is>
-      </c>
-      <c r="V33" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="W33" t="inlineStr">
-        <is>
-          <t>Älvsby</t>
-        </is>
-      </c>
-      <c r="Y33" t="inlineStr">
-        <is>
-          <t>2024-07-28</t>
-        </is>
-      </c>
-      <c r="AA33" t="inlineStr">
-        <is>
-          <t>2024-07-28</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Fjolårssvamp med vit mycelmatta</t>
-        </is>
-      </c>
-      <c r="AD33" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE33" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF33" t="inlineStr"/>
-      <c r="AG33" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT33" t="inlineStr"/>
-      <c r="AW33" t="inlineStr">
-        <is>
-          <t>Linda-Marie Grahn</t>
-        </is>
-      </c>
-      <c r="AX33" t="inlineStr">
-        <is>
-          <t>Linda-Marie Grahn</t>
-        </is>
-      </c>
-      <c r="AY33" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 26733-2024 artfynd.xlsx
+++ b/artfynd/A 26733-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY31"/>
+  <dimension ref="A1:AZ31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110049043</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -875,6 +885,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113888851</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -981,6 +996,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118675972</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1087,6 +1107,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118675979</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1193,6 +1218,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118675975</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1299,6 +1329,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118675986</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1405,6 +1440,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118675974</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1511,6 +1551,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118675987</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1617,6 +1662,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118675985</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1723,6 +1773,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118675991</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1829,6 +1884,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113888852</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1935,6 +1995,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118675981</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2041,6 +2106,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118675988</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2155,6 +2225,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118767586</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2269,6 +2344,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118767587</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2375,6 +2455,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118675990</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2472,6 +2557,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118767585</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2578,6 +2668,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113888853</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2684,6 +2779,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118675973</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2790,6 +2890,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118675983</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2896,6 +3001,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113888850</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3002,6 +3112,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118675969</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3108,6 +3223,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118675971</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3214,6 +3334,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118675980</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3320,6 +3445,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113888849</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3426,6 +3556,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118675970</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3532,6 +3667,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118675978</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3637,6 +3777,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118767584</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3743,6 +3888,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113888848</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3849,8 +3999,45 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118675989</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 26733-2024 artfynd.xlsx
+++ b/artfynd/A 26733-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ31"/>
+  <dimension ref="A1:AZ46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,45 +680,49 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>110049043</v>
+        <v>136348932</v>
       </c>
       <c r="B2" t="n">
-        <v>90932</v>
+        <v>92259</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1962</v>
+        <v>1503</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(P.Karst.) Miettinen</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Rävabacken Utv, Nb</t>
+          <t>Grundsel, Nb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>741888</v>
+        <v>741568</v>
       </c>
       <c r="R2" t="n">
-        <v>7295220</v>
+        <v>7295226</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,12 +749,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-10-07</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-10-07</t>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,24 +774,24 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Robert Sandberg</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Jonas Nordenström</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110049043</t>
+          <t>https://artportalen.se/Sighting/136348932</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113888851</v>
+        <v>110049043</v>
       </c>
       <c r="B3" t="n">
         <v>90932</v>
@@ -810,24 +819,20 @@
           <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Grundsel, Nb</t>
+          <t>Rävabacken Utv, Nb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>741828</v>
+        <v>741888</v>
       </c>
       <c r="R3" t="n">
-        <v>7295240</v>
+        <v>7295220</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -851,17 +856,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-09-25</t>
+          <t>2022-10-07</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-09-25</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2022-10-07</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -876,24 +876,24 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Robert Sandberg</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Jonas Nordenström</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/113888851</t>
+          <t>https://artportalen.se/Sighting/110049043</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118675972</v>
+        <v>113888851</v>
       </c>
       <c r="B4" t="n">
         <v>90932</v>
@@ -932,13 +932,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>741876</v>
+        <v>741828</v>
       </c>
       <c r="R4" t="n">
-        <v>7295224</v>
+        <v>7295240</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -998,13 +998,13 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118675972</t>
+          <t>https://artportalen.se/Sighting/113888851</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118675979</v>
+        <v>118675972</v>
       </c>
       <c r="B5" t="n">
         <v>90932</v>
@@ -1043,10 +1043,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>741829</v>
+        <v>741876</v>
       </c>
       <c r="R5" t="n">
-        <v>7295244</v>
+        <v>7295224</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
+          <t>2023-09-25</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
+          <t>2023-09-25</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1109,38 +1109,38 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118675979</t>
+          <t>https://artportalen.se/Sighting/118675972</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118675975</v>
+        <v>118675979</v>
       </c>
       <c r="B6" t="n">
-        <v>91394</v>
+        <v>90932</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2051</v>
+        <v>1962</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rotfingersvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Ramaria boreimaxima</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; M.Toivonen</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1154,10 +1154,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>741729</v>
+        <v>741829</v>
       </c>
       <c r="R6" t="n">
-        <v>7295267</v>
+        <v>7295244</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-09-25</t>
+          <t>2023-09-28</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-09-25</t>
+          <t>2023-09-28</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1220,13 +1220,13 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118675975</t>
+          <t>https://artportalen.se/Sighting/118675979</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118675986</v>
+        <v>118675975</v>
       </c>
       <c r="B7" t="n">
         <v>91394</v>
@@ -1265,10 +1265,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>741517</v>
+        <v>741729</v>
       </c>
       <c r="R7" t="n">
-        <v>7295299</v>
+        <v>7295267</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1331,16 +1331,16 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118675986</t>
+          <t>https://artportalen.se/Sighting/118675975</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118675974</v>
+        <v>118675986</v>
       </c>
       <c r="B8" t="n">
-        <v>93213</v>
+        <v>91394</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1348,21 +1348,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2059</v>
+        <v>2051</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Rotfingersvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Ramaria boreimaxima</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>Kytöv. &amp; M.Toivonen</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1376,10 +1376,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>741729</v>
+        <v>741517</v>
       </c>
       <c r="R8" t="n">
-        <v>7295267</v>
+        <v>7295299</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1442,13 +1442,13 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118675974</t>
+          <t>https://artportalen.se/Sighting/118675986</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118675987</v>
+        <v>118675974</v>
       </c>
       <c r="B9" t="n">
         <v>93213</v>
@@ -1487,10 +1487,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>741403</v>
+        <v>741729</v>
       </c>
       <c r="R9" t="n">
-        <v>7295287</v>
+        <v>7295267</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1553,38 +1553,38 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118675987</t>
+          <t>https://artportalen.se/Sighting/118675974</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118675985</v>
+        <v>118675987</v>
       </c>
       <c r="B10" t="n">
-        <v>93189</v>
+        <v>93213</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4361</v>
+        <v>2059</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1598,10 +1598,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>741562</v>
+        <v>741403</v>
       </c>
       <c r="R10" t="n">
-        <v>7295281</v>
+        <v>7295287</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1664,38 +1664,38 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118675985</t>
+          <t>https://artportalen.se/Sighting/118675987</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118675991</v>
+        <v>136348931</v>
       </c>
       <c r="B11" t="n">
-        <v>93189</v>
+        <v>93394</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4361</v>
+        <v>2059</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1709,10 +1709,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>741370</v>
+        <v>741560</v>
       </c>
       <c r="R11" t="n">
-        <v>7295400</v>
+        <v>7295225</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1739,12 +1739,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2023-09-25</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2023-09-25</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -1775,16 +1775,16 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118675991</t>
+          <t>https://artportalen.se/Sighting/136348931</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113888852</v>
+        <v>118675985</v>
       </c>
       <c r="B12" t="n">
-        <v>93191</v>
+        <v>93189</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1792,21 +1792,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1820,13 +1820,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>741769</v>
+        <v>741562</v>
       </c>
       <c r="R12" t="n">
-        <v>7295250</v>
+        <v>7295281</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1886,16 +1886,16 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/113888852</t>
+          <t>https://artportalen.se/Sighting/118675985</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118675981</v>
+        <v>118675991</v>
       </c>
       <c r="B13" t="n">
-        <v>93191</v>
+        <v>93189</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1903,21 +1903,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1931,10 +1931,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>741752</v>
+        <v>741370</v>
       </c>
       <c r="R13" t="n">
-        <v>7295263</v>
+        <v>7295400</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1961,12 +1961,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
+          <t>2023-09-25</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
+          <t>2023-09-25</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -1997,16 +1997,16 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118675981</t>
+          <t>https://artportalen.se/Sighting/118675991</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118675988</v>
+        <v>136348925</v>
       </c>
       <c r="B14" t="n">
-        <v>93197</v>
+        <v>93370</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2014,21 +2014,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2042,10 +2042,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>741389</v>
+        <v>741761</v>
       </c>
       <c r="R14" t="n">
-        <v>7295360</v>
+        <v>7295240</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2072,12 +2072,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2023-09-25</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2023-09-25</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2108,16 +2108,16 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118675988</t>
+          <t>https://artportalen.se/Sighting/136348925</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118767586</v>
+        <v>136348926</v>
       </c>
       <c r="B15" t="n">
-        <v>93197</v>
+        <v>93370</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2125,45 +2125,38 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Sikträskberget, Nb</t>
+          <t>Grundsel, Nb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>741962</v>
+        <v>741717</v>
       </c>
       <c r="R15" t="n">
-        <v>7295247</v>
+        <v>7295216</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2190,17 +2183,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-07-28</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-07-28</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Fjolårssvamp med vit mycelmatta</t>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2209,34 +2202,33 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118767586</t>
+          <t>https://artportalen.se/Sighting/136348926</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118767587</v>
+        <v>136348930</v>
       </c>
       <c r="B16" t="n">
-        <v>93197</v>
+        <v>93370</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2244,45 +2236,38 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Sikträskberget, Nb</t>
+          <t>Grundsel, Nb</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>741878</v>
+        <v>741555</v>
       </c>
       <c r="R16" t="n">
-        <v>7295261</v>
+        <v>7295230</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2309,17 +2294,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-07-28</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-07-28</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Fjolårssvamp med vit mycelmatta</t>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2328,56 +2313,55 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118767587</t>
+          <t>https://artportalen.se/Sighting/136348930</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118675990</v>
+        <v>113888852</v>
       </c>
       <c r="B17" t="n">
-        <v>93201</v>
+        <v>93191</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4365</v>
+        <v>4362</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2391,13 +2375,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>741384</v>
+        <v>741769</v>
       </c>
       <c r="R17" t="n">
-        <v>7295367</v>
+        <v>7295250</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2457,51 +2441,55 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118675990</t>
+          <t>https://artportalen.se/Sighting/113888852</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118767585</v>
+        <v>118675981</v>
       </c>
       <c r="B18" t="n">
-        <v>93201</v>
+        <v>93191</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4365</v>
+        <v>4362</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Sikträskberget, Nb</t>
+          <t>Grundsel, Nb</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>741848</v>
+        <v>741752</v>
       </c>
       <c r="R18" t="n">
-        <v>7295262</v>
+        <v>7295263</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2528,12 +2516,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-07-28</t>
+          <t>2023-09-28</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-07-28</t>
+          <t>2023-09-28</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2548,27 +2541,27 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118767585</t>
+          <t>https://artportalen.se/Sighting/118675981</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113888853</v>
+        <v>136348924</v>
       </c>
       <c r="B19" t="n">
-        <v>93209</v>
+        <v>93372</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2576,21 +2569,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4366</v>
+        <v>4362</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2604,13 +2597,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>741744</v>
+        <v>741972</v>
       </c>
       <c r="R19" t="n">
-        <v>7295260</v>
+        <v>7295228</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2634,12 +2627,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2023-09-25</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2023-09-25</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -2670,16 +2663,16 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/113888853</t>
+          <t>https://artportalen.se/Sighting/136348924</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118675973</v>
+        <v>118675988</v>
       </c>
       <c r="B20" t="n">
-        <v>93209</v>
+        <v>93197</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2687,21 +2680,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2715,10 +2708,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>741771</v>
+        <v>741389</v>
       </c>
       <c r="R20" t="n">
-        <v>7295246</v>
+        <v>7295360</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2781,16 +2774,16 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118675973</t>
+          <t>https://artportalen.se/Sighting/118675988</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118675983</v>
+        <v>118767586</v>
       </c>
       <c r="B21" t="n">
-        <v>93209</v>
+        <v>93197</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2798,38 +2791,45 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Grundsel, Nb</t>
+          <t>Sikträskberget, Nb</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>741729</v>
+        <v>741962</v>
       </c>
       <c r="R21" t="n">
-        <v>7295271</v>
+        <v>7295247</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2856,17 +2856,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
+          <t>2024-07-28</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
+          <t>2024-07-28</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>Fjolårssvamp med vit mycelmatta</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2875,33 +2875,34 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118675983</t>
+          <t>https://artportalen.se/Sighting/118767586</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113888850</v>
+        <v>118767587</v>
       </c>
       <c r="B22" t="n">
-        <v>93235</v>
+        <v>93197</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2909,41 +2910,48 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Grundsel, Nb</t>
+          <t>Sikträskberget, Nb</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>741828</v>
+        <v>741878</v>
       </c>
       <c r="R22" t="n">
-        <v>7295240</v>
+        <v>7295261</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2967,17 +2975,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2023-09-25</t>
+          <t>2024-07-28</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2023-09-25</t>
+          <t>2024-07-28</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>Fjolårssvamp med vit mycelmatta</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2986,33 +2994,34 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/113888850</t>
+          <t>https://artportalen.se/Sighting/118767587</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118675969</v>
+        <v>136348929</v>
       </c>
       <c r="B23" t="n">
-        <v>93235</v>
+        <v>93378</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3020,21 +3029,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -3048,10 +3057,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>741737</v>
+        <v>741521</v>
       </c>
       <c r="R23" t="n">
-        <v>7295240</v>
+        <v>7295235</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3078,12 +3087,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2023-09-25</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2023-09-25</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -3114,16 +3123,16 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118675969</t>
+          <t>https://artportalen.se/Sighting/136348929</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>118675971</v>
+        <v>136348936</v>
       </c>
       <c r="B24" t="n">
-        <v>93235</v>
+        <v>93378</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3131,21 +3140,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3159,10 +3168,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>741876</v>
+        <v>741627</v>
       </c>
       <c r="R24" t="n">
-        <v>7295224</v>
+        <v>7295237</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3189,12 +3198,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2023-09-25</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2023-09-25</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
@@ -3225,16 +3234,16 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118675971</t>
+          <t>https://artportalen.se/Sighting/136348936</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>118675980</v>
+        <v>136348937</v>
       </c>
       <c r="B25" t="n">
-        <v>93235</v>
+        <v>93378</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3242,21 +3251,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3270,10 +3279,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>741829</v>
+        <v>741652</v>
       </c>
       <c r="R25" t="n">
-        <v>7295237</v>
+        <v>7295231</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3300,12 +3309,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
@@ -3336,38 +3345,38 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118675980</t>
+          <t>https://artportalen.se/Sighting/136348937</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>113888849</v>
+        <v>118675990</v>
       </c>
       <c r="B26" t="n">
-        <v>79084</v>
+        <v>93201</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6446</v>
+        <v>4365</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -3381,13 +3390,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>741901</v>
+        <v>741384</v>
       </c>
       <c r="R26" t="n">
-        <v>7295230</v>
+        <v>7295367</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3447,55 +3456,51 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/113888849</t>
+          <t>https://artportalen.se/Sighting/118675990</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>118675970</v>
+        <v>118767585</v>
       </c>
       <c r="B27" t="n">
-        <v>79084</v>
+        <v>93201</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6446</v>
+        <v>4365</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst) P.Karst</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Grundsel, Nb</t>
+          <t>Sikträskberget, Nb</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>741875</v>
+        <v>741848</v>
       </c>
       <c r="R27" t="n">
-        <v>7295226</v>
+        <v>7295262</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3522,17 +3527,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2023-09-25</t>
+          <t>2024-07-28</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2023-09-25</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2024-07-28</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3547,49 +3547,49 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118675970</t>
+          <t>https://artportalen.se/Sighting/118767585</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>118675978</v>
+        <v>136348933</v>
       </c>
       <c r="B28" t="n">
-        <v>79084</v>
+        <v>93382</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6446</v>
+        <v>4365</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3603,10 +3603,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>741900</v>
+        <v>741568</v>
       </c>
       <c r="R28" t="n">
-        <v>7295228</v>
+        <v>7295225</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3633,12 +3633,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
@@ -3669,62 +3669,58 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118675978</t>
+          <t>https://artportalen.se/Sighting/136348933</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>118767584</v>
+        <v>113888853</v>
       </c>
       <c r="B29" t="n">
-        <v>57141</v>
+        <v>93209</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100138</v>
+        <v>4366</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Sikträskberget, Nb</t>
+          <t>Grundsel, Nb</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>741762</v>
+        <v>741744</v>
       </c>
       <c r="R29" t="n">
-        <v>7295230</v>
+        <v>7295260</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3748,12 +3744,17 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2024-07-28</t>
+          <t>2023-09-25</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2024-07-28</t>
+          <t>2023-09-25</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3768,49 +3769,49 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118767584</t>
+          <t>https://artportalen.se/Sighting/113888853</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>113888848</v>
+        <v>118675973</v>
       </c>
       <c r="B30" t="n">
-        <v>93228</v>
+        <v>93209</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>232140</v>
+        <v>4366</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3824,13 +3825,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>741479</v>
+        <v>741771</v>
       </c>
       <c r="R30" t="n">
-        <v>7295340</v>
+        <v>7295246</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3890,38 +3891,38 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/113888848</t>
+          <t>https://artportalen.se/Sighting/118675973</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>118675989</v>
+        <v>118675983</v>
       </c>
       <c r="B31" t="n">
-        <v>93228</v>
+        <v>93209</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>232140</v>
+        <v>4366</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3935,10 +3936,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>741385</v>
+        <v>741729</v>
       </c>
       <c r="R31" t="n">
-        <v>7295367</v>
+        <v>7295271</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3965,12 +3966,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2023-09-25</t>
+          <t>2023-09-28</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2023-09-25</t>
+          <t>2023-09-28</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
@@ -4000,6 +4001,1670 @@
       </c>
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118675983</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>136348934</v>
+      </c>
+      <c r="B32" t="n">
+        <v>93390</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Grundsel, Nb</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>741596</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7295229</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136348934</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>136348935</v>
+      </c>
+      <c r="B33" t="n">
+        <v>93390</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Grundsel, Nb</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>741615</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7295225</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136348935</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>136348940</v>
+      </c>
+      <c r="B34" t="n">
+        <v>93390</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Grundsel, Nb</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>741688</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7295226</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136348940</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>136348939</v>
+      </c>
+      <c r="B35" t="n">
+        <v>93022</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>4745</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Tallriska</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Lactarius musteus</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Grundsel, Nb</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>741677</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7295225</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136348939</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>113888850</v>
+      </c>
+      <c r="B36" t="n">
+        <v>93235</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Grundsel, Nb</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>741828</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7295240</v>
+      </c>
+      <c r="S36" t="n">
+        <v>5</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2023-09-25</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2023-09-25</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113888850</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>118675969</v>
+      </c>
+      <c r="B37" t="n">
+        <v>93235</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Grundsel, Nb</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>741737</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7295240</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2023-09-25</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2023-09-25</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118675969</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>118675971</v>
+      </c>
+      <c r="B38" t="n">
+        <v>93235</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Grundsel, Nb</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>741876</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7295224</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2023-09-25</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2023-09-25</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118675971</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>118675980</v>
+      </c>
+      <c r="B39" t="n">
+        <v>93235</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Grundsel, Nb</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>741829</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7295237</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2023-09-28</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2023-09-28</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118675980</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>136348938</v>
+      </c>
+      <c r="B40" t="n">
+        <v>93416</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Grundsel, Nb</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>741673</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7295224</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136348938</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>113888849</v>
+      </c>
+      <c r="B41" t="n">
+        <v>79084</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Grundsel, Nb</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>741901</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7295230</v>
+      </c>
+      <c r="S41" t="n">
+        <v>5</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2023-09-25</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2023-09-25</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113888849</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>118675970</v>
+      </c>
+      <c r="B42" t="n">
+        <v>79084</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Grundsel, Nb</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>741875</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7295226</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2023-09-25</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2023-09-25</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118675970</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>118675978</v>
+      </c>
+      <c r="B43" t="n">
+        <v>79084</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Grundsel, Nb</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>741900</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7295228</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2023-09-28</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2023-09-28</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118675978</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>118767584</v>
+      </c>
+      <c r="B44" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Sikträskberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>741762</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7295230</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2024-07-28</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2024-07-28</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118767584</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>113888848</v>
+      </c>
+      <c r="B45" t="n">
+        <v>93228</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>232140</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Tajgataggsvamp</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Phellodon secretus</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Niemelä &amp; Kinnunen</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Grundsel, Nb</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>741479</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7295340</v>
+      </c>
+      <c r="S45" t="n">
+        <v>5</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2023-09-25</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2023-09-25</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113888848</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>118675989</v>
+      </c>
+      <c r="B46" t="n">
+        <v>93228</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>232140</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Tajgataggsvamp</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Phellodon secretus</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Niemelä &amp; Kinnunen</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Grundsel, Nb</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>741385</v>
+      </c>
+      <c r="R46" t="n">
+        <v>7295367</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2023-09-25</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2023-09-25</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/118675989</t>
         </is>
@@ -4037,6 +5702,21 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
